--- a/sources/table_normalization/xlsx/employment-table13.xlsx
+++ b/sources/table_normalization/xlsx/employment-table13.xlsx
@@ -238,7 +238,6 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -248,6 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -555,17 +555,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -573,28 +573,28 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
+      <c r="A5" s="5"/>
       <c r="B5">
         <v>2022</v>
       </c>
@@ -708,7 +708,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="7" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="7" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1922,56 +1922,56 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="10">
